--- a/artfynd/A 59837-2020 artfynd.xlsx
+++ b/artfynd/A 59837-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59837-2020 artfynd.xlsx
+++ b/artfynd/A 59837-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1065,6 +1065,139 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121404791</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106621</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Valdemarsviks ishall SV, 50 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593635</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6453756</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Valdemarsvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Valdemarsvik</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>E-Val-0147</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vinterståndarna fanns spridda nedanför skogsbacken inom ett triangelformat platt område bakom ishallen. 3 av dem hittades i slänten på andra sidan grusvägen. Slyröjning gjordes i överenskommelse med markägaren för att förbättra skogsklockornas förutsättningar.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gabriella Gelland</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gabriella Gelland, Knut Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59837-2020 artfynd.xlsx
+++ b/artfynd/A 59837-2020 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>121404791</v>
       </c>
       <c r="B5" t="n">
-        <v>106621</v>
+        <v>106634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59837-2020 artfynd.xlsx
+++ b/artfynd/A 59837-2020 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>121404791</v>
       </c>
       <c r="B5" t="n">
-        <v>106634</v>
+        <v>106635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59837-2020 artfynd.xlsx
+++ b/artfynd/A 59837-2020 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>121404791</v>
       </c>
       <c r="B5" t="n">
-        <v>106635</v>
+        <v>106638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59837-2020 artfynd.xlsx
+++ b/artfynd/A 59837-2020 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>121404791</v>
       </c>
       <c r="B5" t="n">
-        <v>106638</v>
+        <v>106644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59837-2020 artfynd.xlsx
+++ b/artfynd/A 59837-2020 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>121404791</v>
       </c>
       <c r="B5" t="n">
-        <v>106644</v>
+        <v>106645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59837-2020 artfynd.xlsx
+++ b/artfynd/A 59837-2020 artfynd.xlsx
@@ -1070,7 +1070,7 @@
         <v>121404791</v>
       </c>
       <c r="B5" t="n">
-        <v>106645</v>
+        <v>106653</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59837-2020 artfynd.xlsx
+++ b/artfynd/A 59837-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1065,139 +1065,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>121404791</v>
-      </c>
-      <c r="B5" t="n">
-        <v>106653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>245</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Campanula cervicaria</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Valdemarsviks ishall SV, 50 m, Ög</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>593635</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6453756</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Valdemarsvik</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Valdemarsvik</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>E-Val-0147</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vinterståndarna fanns spridda nedanför skogsbacken inom ett triangelformat platt område bakom ishallen. 3 av dem hittades i slänten på andra sidan grusvägen. Slyröjning gjordes i överenskommelse med markägaren för att förbättra skogsklockornas förutsättningar.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Gabriella Gelland</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Gabriella Gelland, Knut Eriksson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
